--- a/exports/TVSMOTOR_full_report.xlsx
+++ b/exports/TVSMOTOR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>648.7</v>
+        <v>630.15</v>
       </c>
       <c r="I2" t="n">
         <v>631.7459182545248</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.35</v>
+        <v>-3.2</v>
       </c>
       <c r="L2" t="n">
-        <v>3.22</v>
+        <v>3.64</v>
       </c>
       <c r="M2" t="n">
         <v>0.58</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>7.48</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44594.55208333334</v>
+        <v>44595.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>628.05</v>
+        <v>658.85</v>
       </c>
       <c r="I3" t="n">
         <v>652.4534542435146</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>0.33</v>
+        <v>-4.55</v>
       </c>
       <c r="L3" t="n">
-        <v>3.29</v>
+        <v>5.21</v>
       </c>
       <c r="M3" t="n">
         <v>1.43</v>
       </c>
       <c r="N3" t="n">
-        <v>3.61</v>
+        <v>4.05</v>
       </c>
       <c r="O3" t="n">
         <v>-0.5600000000000001</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.63</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44616.38541666666</v>
+        <v>44616.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>632.7</v>
+        <v>619.4</v>
       </c>
       <c r="I4" t="n">
         <v>628.0112469822152</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.97</v>
+        <v>-5.99</v>
       </c>
       <c r="L4" t="n">
-        <v>5.48</v>
+        <v>6.53</v>
       </c>
       <c r="M4" t="n">
         <v>2.9</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44631.38541666666</v>
+        <v>44631.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>574.5</v>
+        <v>583</v>
       </c>
       <c r="I5" t="n">
         <v>580.1969341271962</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>7.25</v>
+        <v>5.88</v>
       </c>
       <c r="L5" t="n">
         <v>2.99</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44683.55208333334</v>
+        <v>44685.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>649.2</v>
+        <v>640.7</v>
       </c>
       <c r="I6" t="n">
         <v>641.8356380686573</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>52</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K6" t="n">
-        <v>11.36</v>
+        <v>9.9</v>
       </c>
       <c r="L6" t="n">
         <v>2.39</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>7.91</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44697.38541666666</v>
+        <v>44697.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="I7" t="n">
         <v>646.916567026679</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.83</v>
+        <v>-1.76</v>
       </c>
       <c r="L7" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.66</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>941.45</v>
+        <v>937.1</v>
       </c>
       <c r="I8" t="n">
         <v>937.7140034100869</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>97.83333333333333</v>
+        <v>98</v>
       </c>
       <c r="K8" t="n">
-        <v>44.39</v>
+        <v>43.73</v>
       </c>
       <c r="L8" t="n">
         <v>1.06</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>5.06</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44803.38541666666</v>
+        <v>44803.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>981</v>
+        <v>986.5</v>
       </c>
       <c r="I9" t="n">
         <v>984.561467217366</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.68</v>
+        <v>-5.27</v>
       </c>
       <c r="L9" t="n">
-        <v>4.86</v>
+        <v>5.62</v>
       </c>
       <c r="M9" t="n">
         <v>0.79</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.75</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44832.55208333334</v>
+        <v>44833.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1021</v>
+        <v>1016.75</v>
       </c>
       <c r="I10" t="n">
         <v>1018.830456780948</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="L10" t="n">
         <v>0.86</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>6.88</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1035.8</v>
+        <v>1073</v>
       </c>
       <c r="I11" t="n">
         <v>1061.961508057893</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.87</v>
+        <v>-5.53</v>
       </c>
       <c r="L11" t="n">
-        <v>2.17</v>
+        <v>5.58</v>
       </c>
       <c r="M11" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" t="n">
-        <v>3.94</v>
+        <v>4.29</v>
       </c>
       <c r="O11" t="n">
         <v>-0.87</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.23</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44869.55208333334</v>
+        <v>44872.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1116.9</v>
+        <v>1090.75</v>
       </c>
       <c r="I12" t="n">
         <v>1099.63661273752</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K12" t="n">
-        <v>4.09</v>
+        <v>1.65</v>
       </c>
       <c r="L12" t="n">
         <v>3.29</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.98</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44922.55208333334</v>
+        <v>44923.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1047</v>
+        <v>1076.05</v>
       </c>
       <c r="I13" t="n">
         <v>1061.787617479448</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K13" t="n">
-        <v>4.01</v>
+        <v>1.35</v>
       </c>
       <c r="L13" t="n">
         <v>6.9</v>
@@ -1182,7 +1337,7 @@
         <v>2.47</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="O13" t="n">
         <v>-0.41</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.77</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44929.55208333334</v>
+        <v>44930.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1042.5</v>
+        <v>1027.95</v>
       </c>
       <c r="I14" t="n">
         <v>1035.011535156417</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.12</v>
+        <v>-4.47</v>
       </c>
       <c r="L14" t="n">
-        <v>3.84</v>
+        <v>4.61</v>
       </c>
       <c r="M14" t="n">
         <v>0.47</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>7.05</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>979.4</v>
+        <v>1032.6</v>
       </c>
       <c r="I15" t="n">
         <v>1026.657174081808</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
-        <v>4.72</v>
+        <v>-0.45</v>
       </c>
       <c r="L15" t="n">
         <v>2.19</v>
       </c>
       <c r="M15" t="n">
-        <v>0.68</v>
+        <v>1.59</v>
       </c>
       <c r="N15" t="n">
-        <v>1.18</v>
+        <v>5.76</v>
       </c>
       <c r="O15" t="n">
         <v>-1.87</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>7.53</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1106</v>
+        <v>1064</v>
       </c>
       <c r="I16" t="n">
         <v>1068.277167150465</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K16" t="n">
-        <v>7.11</v>
+        <v>3.04</v>
       </c>
       <c r="L16" t="n">
         <v>4.12</v>
       </c>
       <c r="M16" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="N16" t="n">
         <v>2.14</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.34</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1075</v>
+        <v>1082.15</v>
       </c>
       <c r="I17" t="n">
         <v>1081.471305873791</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.03</v>
+        <v>-1.71</v>
       </c>
       <c r="L17" t="n">
         <v>4.61</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.49</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45036.55208333334</v>
+        <v>45037.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1125.5</v>
+        <v>1090.25</v>
       </c>
       <c r="I18" t="n">
         <v>1120.405977749486</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>4.01</v>
+        <v>0.75</v>
       </c>
       <c r="L18" t="n">
         <v>0.46</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>7.53</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1138.8</v>
+        <v>1160.65</v>
       </c>
       <c r="I19" t="n">
         <v>1151.639430199607</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.45</v>
+        <v>-6.46</v>
       </c>
       <c r="L19" t="n">
-        <v>4.71</v>
+        <v>6.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="N19" t="n">
-        <v>1.16</v>
+        <v>1.86</v>
       </c>
       <c r="O19" t="n">
         <v>-2.87</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.31</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45100.55208333334</v>
+        <v>45103.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1304.5</v>
+        <v>1291.95</v>
       </c>
       <c r="I20" t="n">
         <v>1295.316213394661</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K20" t="n">
-        <v>12.39</v>
+        <v>11.31</v>
       </c>
       <c r="L20" t="n">
         <v>2.03</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.09</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45117.55208333334</v>
+        <v>45118.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1310.35</v>
+        <v>1348</v>
       </c>
       <c r="I21" t="n">
         <v>1344.976589306767</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.42</v>
+        <v>-4.34</v>
       </c>
       <c r="L21" t="n">
-        <v>3.94</v>
+        <v>4.88</v>
       </c>
       <c r="M21" t="n">
         <v>0.7</v>
       </c>
       <c r="N21" t="n">
-        <v>1.69</v>
+        <v>2.87</v>
       </c>
       <c r="O21" t="n">
         <v>-1.11</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.79</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45315.55208333334</v>
+        <v>45316.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>2009</v>
+        <v>1939.3</v>
       </c>
       <c r="I22" t="n">
         <v>1987.779509421921</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>197.1666666666667</v>
+        <v>198</v>
       </c>
       <c r="K22" t="n">
-        <v>49.04</v>
+        <v>43.86</v>
       </c>
       <c r="L22" t="n">
         <v>3.93</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>271</v>
+        <v>272</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45328.55208333334</v>
+        <v>45329.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2048</v>
+        <v>2068.55</v>
       </c>
       <c r="I23" t="n">
         <v>2062.260022601924</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.61</v>
+        <v>-6.66</v>
       </c>
       <c r="L23" t="n">
         <v>7.13</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.64</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>2166.65</v>
+        <v>2137.8</v>
       </c>
       <c r="I24" t="n">
         <v>2145.90800308718</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>4.74</v>
+        <v>3.35</v>
       </c>
       <c r="L24" t="n">
         <v>3.04</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.34</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45407.38541666666</v>
+        <v>45407.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1995.9</v>
+        <v>2011</v>
       </c>
       <c r="I25" t="n">
         <v>2006.838642162805</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>42.83333333333334</v>
+        <v>43</v>
       </c>
       <c r="K25" t="n">
-        <v>6.64</v>
+        <v>5.93</v>
       </c>
       <c r="L25" t="n">
         <v>2.94</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>5.7</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>2055</v>
+        <v>1982.6</v>
       </c>
       <c r="I26" t="n">
         <v>1984.238037826717</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>2.19</v>
+        <v>-1.41</v>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="M26" t="n">
         <v>0.2</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
         <v>2.36</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>7.78</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>2018</v>
+        <v>2074.7</v>
       </c>
       <c r="I27" t="n">
         <v>2067.868008997858</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.79</v>
+        <v>-4.65</v>
       </c>
       <c r="L27" t="n">
-        <v>4.16</v>
+        <v>7.08</v>
       </c>
       <c r="M27" t="n">
         <v>0.39</v>
       </c>
       <c r="N27" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="O27" t="n">
         <v>-3.8</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.11</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45468.55208333334</v>
+        <v>45469.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>2416.9</v>
+        <v>2375.2</v>
       </c>
       <c r="I28" t="n">
         <v>2378.830237922165</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K28" t="n">
-        <v>16.49</v>
+        <v>14.48</v>
       </c>
       <c r="L28" t="n">
         <v>4.78</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.96</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45478.38541666666</v>
+        <v>45478.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>2411.95</v>
+        <v>2429</v>
       </c>
       <c r="I29" t="n">
         <v>2428.325461959073</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.55</v>
+        <v>-2.27</v>
       </c>
       <c r="L29" t="n">
-        <v>1.97</v>
+        <v>2.69</v>
       </c>
       <c r="M29" t="n">
         <v>0.68</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.13</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>2844.45</v>
+        <v>2735.4</v>
       </c>
       <c r="I30" t="n">
         <v>2792.809511073676</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>88</v>
+        <v>89.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>17.1</v>
+        <v>12.61</v>
       </c>
       <c r="L30" t="n">
         <v>2.84</v>
       </c>
       <c r="M30" t="n">
-        <v>1.95</v>
+        <v>2.93</v>
       </c>
       <c r="N30" t="n">
-        <v>3.33</v>
+        <v>4.03</v>
       </c>
       <c r="O30" t="n">
         <v>2.53</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>7.3</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45576.55208333334</v>
+        <v>45579.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>2792.85</v>
+        <v>2807.95</v>
       </c>
       <c r="I31" t="n">
         <v>2796.957709894789</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.1</v>
+        <v>-2.65</v>
       </c>
       <c r="L31" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="M31" t="n">
         <v>0.54</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.92</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45582.38541666666</v>
+        <v>45582.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>2705.3</v>
+        <v>2679</v>
       </c>
       <c r="I32" t="n">
         <v>2703.821554456573</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.66</v>
+        <v>-4.59</v>
       </c>
       <c r="L32" t="n">
         <v>7.6</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.46</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45628.55208333334</v>
+        <v>45629.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>2482.9</v>
+        <v>2528.15</v>
       </c>
       <c r="I33" t="n">
         <v>2518.438500384321</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K33" t="n">
-        <v>7.32</v>
+        <v>5.63</v>
       </c>
       <c r="L33" t="n">
         <v>3.47</v>
@@ -2322,7 +2717,7 @@
         <v>1.97</v>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
         <v>-3.16</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>4.68</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>2451.15</v>
+        <v>2421.2</v>
       </c>
       <c r="I34" t="n">
         <v>2429.101078957578</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.05</v>
+        <v>-4.23</v>
       </c>
       <c r="L34" t="n">
-        <v>4.16</v>
+        <v>4.39</v>
       </c>
       <c r="M34" t="n">
         <v>1.41</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>5.8</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>2402.1</v>
+        <v>2489.3</v>
       </c>
       <c r="I35" t="n">
         <v>2478.494617445767</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K35" t="n">
-        <v>0.79</v>
+        <v>-2.81</v>
       </c>
       <c r="L35" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="M35" t="n">
         <v>0.77</v>
       </c>
       <c r="N35" t="n">
-        <v>1.87</v>
+        <v>4.41</v>
       </c>
       <c r="O35" t="n">
         <v>-2.5</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>6.88</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>2371.4</v>
+        <v>2347.7</v>
       </c>
       <c r="I36" t="n">
         <v>2348.161917094449</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.74</v>
+        <v>-5.69</v>
       </c>
       <c r="L36" t="n">
-        <v>4.92</v>
+        <v>5.75</v>
       </c>
       <c r="M36" t="n">
         <v>-0</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.9</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45685.38541666666</v>
+        <v>45685.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>2264.4</v>
+        <v>2350</v>
       </c>
       <c r="I37" t="n">
         <v>2330.401178836742</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>3.55</v>
+        <v>-0.1</v>
       </c>
       <c r="L37" t="n">
         <v>2.01</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.76</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45701.55208333334</v>
+        <v>45702.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>2471.4</v>
+        <v>2393.25</v>
       </c>
       <c r="I38" t="n">
         <v>2455.639461254907</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>5.17</v>
+        <v>1.84</v>
       </c>
       <c r="L38" t="n">
         <v>3.79</v>
@@ -2607,7 +3062,7 @@
         <v>0.42</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="O38" t="n">
         <v>5.06</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45736.55208333334</v>
+        <v>45737.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>2343</v>
+        <v>2445.8</v>
       </c>
       <c r="I39" t="n">
         <v>2383.205746198727</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K39" t="n">
-        <v>2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="L39" t="n">
         <v>3.86</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.4</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>2467.55</v>
+        <v>2333.85</v>
       </c>
       <c r="I40" t="n">
         <v>2357.429194710299</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>0.89</v>
+        <v>-4.58</v>
       </c>
       <c r="L40" t="n">
-        <v>3.91</v>
+        <v>9.19</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5</v>
+        <v>9.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.36</v>
+        <v>3.46</v>
       </c>
       <c r="O40" t="n">
         <v>3.07</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.59</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45758.38541666666</v>
+        <v>45758.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>2510.45</v>
+        <v>2516.1</v>
       </c>
       <c r="I41" t="n">
         <v>2511.099267056192</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.57</v>
+        <v>-7.81</v>
       </c>
       <c r="L41" t="n">
         <v>8.4</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.8</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2828</v>
+        <v>2764.1</v>
       </c>
       <c r="I42" t="n">
         <v>2818.104119697643</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>90</v>
+        <v>90.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>12.4</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>0.5600000000000001</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>4.96</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45852.55208333334</v>
+        <v>45853.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2807</v>
+        <v>2890.8</v>
       </c>
       <c r="I43" t="n">
         <v>2858.386744124035</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.55</v>
+        <v>-4.58</v>
       </c>
       <c r="L43" t="n">
-        <v>2.34</v>
+        <v>4.98</v>
       </c>
       <c r="M43" t="n">
         <v>0.09</v>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="O43" t="n">
         <v>-2.69</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>5.76</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>2794</v>
+        <v>2744.1</v>
       </c>
       <c r="I44" t="n">
         <v>2781.682304765979</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.35</v>
+        <v>-5.07</v>
       </c>
       <c r="L44" t="n">
-        <v>3.76</v>
+        <v>5.61</v>
       </c>
       <c r="M44" t="n">
         <v>0.25</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>4.72</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45870.55208333334</v>
+        <v>45873.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>2870</v>
+        <v>2954</v>
       </c>
       <c r="I45" t="n">
         <v>2873.597461296374</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.59</v>
+        <v>-7.65</v>
       </c>
       <c r="L45" t="n">
-        <v>5.1</v>
+        <v>8.16</v>
       </c>
       <c r="M45" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="N45" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="O45" t="n">
         <v>-0.75</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.46</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>3445</v>
+        <v>3409.6</v>
       </c>
       <c r="I46" t="n">
         <v>3437.119974410299</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K46" t="n">
-        <v>16.62</v>
+        <v>15.42</v>
       </c>
       <c r="L46" t="n">
         <v>2.42</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>4.51</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>3502</v>
+        <v>3558</v>
       </c>
       <c r="I47" t="n">
         <v>3537.169611838731</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.71</v>
+        <v>-4.35</v>
       </c>
       <c r="L47" t="n">
-        <v>3.88</v>
+        <v>4.5</v>
       </c>
       <c r="M47" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="N47" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="O47" t="n">
         <v>-1.02</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>4.41</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>3548</v>
+        <v>3495</v>
       </c>
       <c r="I48" t="n">
         <v>3532.851864606082</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.28</v>
+        <v>-1.77</v>
       </c>
       <c r="L48" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="M48" t="n">
         <v>0.3</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.76</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45987.38541666666</v>
+        <v>45987.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>3512</v>
+        <v>3539</v>
       </c>
       <c r="I49" t="n">
         <v>3516.147771222012</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.49</v>
+        <v>-1.26</v>
       </c>
       <c r="L49" t="n">
         <v>3.4</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>3.89</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>3775.9</v>
+        <v>3709.4</v>
       </c>
       <c r="I50" t="n">
         <v>3724.21469559332</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>44</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K50" t="n">
-        <v>6.69</v>
+        <v>4.81</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>0.53</v>
+        <v>0.79</v>
       </c>
       <c r="N50" t="n">
         <v>1.66</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.52</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46059.38541666666</v>
+        <v>46059.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>3705.2</v>
+        <v>3752</v>
       </c>
       <c r="I51" t="n">
         <v>3741.559237927263</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>0.11</v>
+        <v>-1.15</v>
       </c>
       <c r="L51" t="n">
         <v>2.98</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>5.96</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>3866</v>
+        <v>3775.8</v>
       </c>
       <c r="I52" t="n">
         <v>3779.388468398958</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>3.04</v>
+        <v>0.63</v>
       </c>
       <c r="L52" t="n">
         <v>1.37</v>
       </c>
       <c r="M52" t="n">
-        <v>0.44</v>
+        <v>2.22</v>
       </c>
       <c r="N52" t="n">
         <v>2.37</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.97</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>3478</v>
+        <v>3694.1</v>
       </c>
       <c r="I53" t="n">
         <v>3571.719365139417</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K53" t="n">
-        <v>7.89</v>
+        <v>2.16</v>
       </c>
       <c r="L53" t="n">
         <v>3.48</v>
       </c>
       <c r="M53" t="n">
-        <v>2.24</v>
+        <v>4.66</v>
       </c>
       <c r="N53" t="n">
-        <v>3.99</v>
+        <v>6.43</v>
       </c>
       <c r="O53" t="n">
         <v>-1.65</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46134.55208333334</v>
+        <v>46135.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>3655.3</v>
+        <v>3504</v>
       </c>
       <c r="I54" t="n">
         <v>3594.464461538188</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.05</v>
+        <v>-5.15</v>
       </c>
       <c r="L54" t="n">
-        <v>3.25</v>
+        <v>5.58</v>
       </c>
       <c r="M54" t="n">
         <v>1.75</v>
       </c>
       <c r="N54" t="n">
-        <v>2.72</v>
+        <v>3.84</v>
       </c>
       <c r="O54" t="n">
         <v>6.43</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>7.81</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>3618</v>
+        <v>3724.2</v>
       </c>
       <c r="I55" t="n">
         <v>3669.541228339395</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.25</v>
+        <v>-6.28</v>
       </c>
       <c r="L55" t="n">
-        <v>3.77</v>
+        <v>6.45</v>
       </c>
       <c r="M55" t="n">
         <v>1.22</v>
       </c>
       <c r="N55" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="O55" t="n">
         <v>-3.84</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>8.26</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46155.55208333334</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>3523</v>
+        <v>3439.2</v>
       </c>
       <c r="I56" t="n">
         <v>3483.659984941094</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.4</v>
+        <v>-7.65</v>
       </c>
       <c r="L56" t="n">
-        <v>6.48</v>
+        <v>9.17</v>
       </c>
       <c r="M56" t="n">
         <v>1.44</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>3315</v>
+        <v>3462</v>
       </c>
       <c r="I57" t="n">
         <v>3449.961732109517</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K57" t="n">
-        <v>3.61</v>
+        <v>-0.66</v>
       </c>
       <c r="L57" t="n">
         <v>3.04</v>
       </c>
       <c r="M57" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="N57" t="n">
-        <v>2.4</v>
+        <v>4.19</v>
       </c>
       <c r="O57" t="n">
         <v>-1.65</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.63</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46261.55208333334</v>
+        <v>46262.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>4400.8</v>
+        <v>4243.2</v>
       </c>
       <c r="I58" t="n">
         <v>4314.487884389446</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K58" t="n">
-        <v>27.12</v>
+        <v>22.56</v>
       </c>
       <c r="L58" t="n">
         <v>3.73</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.12</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>3950</v>
+        <v>4051.5</v>
       </c>
       <c r="I59" t="n">
         <v>4044.657402040973</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K59" t="n">
-        <v>6.91</v>
+        <v>4.52</v>
       </c>
       <c r="L59" t="n">
         <v>4.28</v>
@@ -3804,7 +4511,7 @@
         <v>0.68</v>
       </c>
       <c r="N59" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O59" t="n">
         <v>-2.43</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3864,6 +4583,14 @@
       <c r="Q60" t="n">
         <v>18</v>
       </c>
+      <c r="R60" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5966,7 +6693,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -5976,7 +6703,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -5986,7 +6713,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>197.2</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
@@ -5996,7 +6723,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6006,7 +6733,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="10">
@@ -6016,7 +6743,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="11">
@@ -6026,7 +6753,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -6036,7 +6763,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6046,7 +6773,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67.2</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="14">
@@ -6056,7 +6783,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.95</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="15">
@@ -6066,7 +6793,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.56</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="16">
@@ -6076,7 +6803,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.34</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="17">
@@ -6086,7 +6813,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49.04</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="18">
@@ -6096,7 +6823,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.2</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="19">
@@ -6106,7 +6833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.47</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="20">
@@ -6116,7 +6843,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="21">
@@ -6126,7 +6853,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.4</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="22">
@@ -6136,7 +6863,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -6156,7 +6883,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="25">
@@ -6166,7 +6893,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.45</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="26">
@@ -6176,7 +6903,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.82</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="27">
@@ -6186,7 +6913,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.06</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="28">
@@ -6196,7 +6923,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
